--- a/data/trans_orig/P33B3_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P33B3_2023-Habitat-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Poblacion según la frecuencia con la que se despierta demasiado temprano de forma involuntaria en 2023</t>
+          <t>Poblacion según la frecuencia con la que se despierta demasiado temprano de forma involuntaria en 2023 (tasa de respuesta: 99,97%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>36026</t>
+          <t>36023</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>62548</t>
+          <t>62771</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>56726</t>
+          <t>58468</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>81663</t>
+          <t>81893</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>100337</t>
+          <t>101332</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>135209</t>
+          <t>134640</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,28%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>34110</t>
+          <t>34225</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>59921</t>
+          <t>59992</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>70693</t>
+          <t>72043</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>97486</t>
+          <t>97319</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>111473</t>
+          <t>111892</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>150027</t>
+          <t>149156</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,39%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>100225</t>
+          <t>100530</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>139263</t>
+          <t>137192</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>21,95%</t>
+          <t>21,63%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>155215</t>
+          <t>154656</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>190525</t>
+          <t>190195</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>22,98%</t>
+          <t>22,9%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>28,21%</t>
+          <t>28,16%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>265095</t>
+          <t>263366</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>317390</t>
+          <t>315546</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>20,11%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>24,23%</t>
+          <t>24,09%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>395978</t>
+          <t>394266</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>445970</t>
+          <t>448385</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>62,42%</t>
+          <t>62,15%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>70,3%</t>
+          <t>70,68%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>330043</t>
+          <t>331383</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>371902</t>
+          <t>371467</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>48,87%</t>
+          <t>49,07%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>55,07%</t>
+          <t>55,0%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>740940</t>
+          <t>741401</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>807980</t>
+          <t>806020</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>56,57%</t>
+          <t>56,6%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>61,69%</t>
+          <t>61,54%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>40654</t>
+          <t>40286</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>108973</t>
+          <t>112039</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>94965</t>
+          <t>94201</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>124647</t>
+          <t>125257</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>126585</t>
+          <t>125571</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>223455</t>
+          <t>222678</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,36%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>33251</t>
+          <t>33484</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>91040</t>
+          <t>94022</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>88620</t>
+          <t>87305</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>118430</t>
+          <t>119896</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>112650</t>
+          <t>108920</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>198947</t>
+          <t>199331</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,27%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>73683</t>
+          <t>64213</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>180354</t>
+          <t>180023</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>201983</t>
+          <t>200699</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>244987</t>
+          <t>241819</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>20,95%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>25,57%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>233014</t>
+          <t>243282</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>412990</t>
+          <t>418363</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>19,46%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>825649</t>
+          <t>822346</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1040649</t>
+          <t>1063336</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>69,27%</t>
+          <t>68,99%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>87,31%</t>
+          <t>89,21%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>498482</t>
+          <t>500155</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>549885</t>
+          <t>552665</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>52,03%</t>
+          <t>52,2%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>57,39%</t>
+          <t>57,68%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1326442</t>
+          <t>1328133</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1667109</t>
+          <t>1676785</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>61,69%</t>
+          <t>61,77%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>77,54%</t>
+          <t>77,99%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>34084</t>
+          <t>34352</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>61559</t>
+          <t>63992</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>29818</t>
+          <t>26627</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>78840</t>
+          <t>78358</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>64002</t>
+          <t>70723</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>126074</t>
+          <t>131204</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>8,01%</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>29531</t>
+          <t>29572</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>54074</t>
+          <t>53836</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>41012</t>
+          <t>35847</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>103260</t>
+          <t>103034</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>76420</t>
+          <t>74464</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>140785</t>
+          <t>140993</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,61%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>111839</t>
+          <t>111986</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>157868</t>
+          <t>162107</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>23,0%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>64448</t>
+          <t>59967</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>159981</t>
+          <t>161489</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>170795</t>
+          <t>162135</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>304146</t>
+          <t>302804</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>18,49%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>455061</t>
+          <t>455108</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>509083</t>
+          <t>509951</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2227,7 +2227,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>72,24%</t>
+          <t>72,37%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>599115</t>
+          <t>599720</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>792598</t>
+          <t>807164</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>64,19%</t>
+          <t>64,25%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>84,92%</t>
+          <t>86,48%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1081679</t>
+          <t>1083070</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1314694</t>
+          <t>1328078</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>66,03%</t>
+          <t>66,12%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>80,26%</t>
+          <t>81,08%</t>
         </is>
       </c>
     </row>
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>75731</t>
+          <t>73196</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>113940</t>
+          <t>111181</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>95294</t>
+          <t>95298</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>139166</t>
+          <t>142906</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2492,7 +2492,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>180922</t>
+          <t>182034</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>240497</t>
+          <t>239036</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>11,84%</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>65206</t>
+          <t>66522</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>99904</t>
+          <t>101777</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>96397</t>
+          <t>97456</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>138852</t>
+          <t>140694</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>173606</t>
+          <t>176318</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>229753</t>
+          <t>231188</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>11,45%</t>
         </is>
       </c>
     </row>
@@ -2663,12 +2663,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>124389</t>
+          <t>126450</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>165384</t>
+          <t>169399</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>18,28%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>144213</t>
+          <t>149881</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>209599</t>
+          <t>209767</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>19,2%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>288952</t>
+          <t>293251</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>362587</t>
+          <t>365496</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>18,1%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>581759</t>
+          <t>576538</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>639886</t>
+          <t>637736</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>62,77%</t>
+          <t>62,21%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>69,04%</t>
+          <t>68,81%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>627814</t>
+          <t>625063</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>751179</t>
+          <t>750717</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>57,46%</t>
+          <t>57,21%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>68,75%</t>
+          <t>68,71%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1227941</t>
+          <t>1225655</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1365067</t>
+          <t>1362434</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>60,81%</t>
+          <t>60,69%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>67,6%</t>
+          <t>67,47%</t>
         </is>
       </c>
     </row>
@@ -3006,12 +3006,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>211610</t>
+          <t>202431</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>303189</t>
+          <t>305232</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3021,12 +3021,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>284318</t>
+          <t>289864</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>393181</t>
+          <t>393274</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3076,12 +3076,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>545353</t>
+          <t>534790</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>677308</t>
+          <t>679143</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,54%</t>
         </is>
       </c>
     </row>
@@ -3119,12 +3119,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>179675</t>
+          <t>187849</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>273694</t>
+          <t>271955</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3154,12 +3154,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>303510</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>420014</t>
+          <t>421723</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3189,12 +3189,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>535011</t>
+          <t>534577</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>673845</t>
+          <t>674359</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3204,7 +3204,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3232,12 +3232,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>411403</t>
+          <t>416339</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>594409</t>
+          <t>596112</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3247,12 +3247,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>17,24%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3267,12 +3267,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>564177</t>
+          <t>569538</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>763656</t>
+          <t>763516</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>20,86%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3302,12 +3302,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1063379</t>
+          <t>1066915</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1324425</t>
+          <t>1322797</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>18,59%</t>
         </is>
       </c>
     </row>
@@ -3345,12 +3345,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2325331</t>
+          <t>2323094</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2671353</t>
+          <t>2679751</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3360,12 +3360,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>67,25%</t>
+          <t>67,18%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>77,26%</t>
+          <t>77,5%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>2104171</t>
+          <t>2108351</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>2498472</t>
+          <t>2476478</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3395,12 +3395,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>57,5%</t>
+          <t>57,61%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>68,27%</t>
+          <t>67,67%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>4490376</t>
+          <t>4490366</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>4979233</t>
+          <t>4975461</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3435,7 +3435,7 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>69,96%</t>
+          <t>69,91%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P33B3_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P33B3_2023-Habitat-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>47431</t>
+          <t>52076</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>36023</t>
+          <t>40563</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>62771</t>
+          <t>68903</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>68614</t>
+          <t>76419</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>58468</t>
+          <t>64700</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>81893</t>
+          <t>91682</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>116046</t>
+          <t>128495</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>101332</t>
+          <t>109525</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>134640</t>
+          <t>147722</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,39%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>45589</t>
+          <t>49381</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>34225</t>
+          <t>37440</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>59992</t>
+          <t>67592</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>82984</t>
+          <t>90901</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>72043</t>
+          <t>76552</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>97319</t>
+          <t>105542</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>128573</t>
+          <t>140281</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>111892</t>
+          <t>121702</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>149156</t>
+          <t>162990</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,46%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>118636</t>
+          <t>128414</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>100530</t>
+          <t>110480</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>137192</t>
+          <t>149290</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>21,63%</t>
+          <t>21,65%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>171559</t>
+          <t>180372</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>154656</t>
+          <t>162950</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>190195</t>
+          <t>197761</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>25,4%</t>
+          <t>24,62%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>22,9%</t>
+          <t>22,24%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>28,16%</t>
+          <t>26,99%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>290195</t>
+          <t>308787</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>263366</t>
+          <t>281817</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>315546</t>
+          <t>340584</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>21,71%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>24,09%</t>
+          <t>23,95%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>422755</t>
+          <t>459756</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>394266</t>
+          <t>434534</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>448385</t>
+          <t>485216</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>66,64%</t>
+          <t>66,67%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>62,15%</t>
+          <t>63,01%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>70,68%</t>
+          <t>70,36%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>352213</t>
+          <t>385030</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>331383</t>
+          <t>362821</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>371467</t>
+          <t>406485</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>52,15%</t>
+          <t>52,55%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>49,07%</t>
+          <t>49,52%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>55,0%</t>
+          <t>55,48%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>774968</t>
+          <t>844787</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>741401</t>
+          <t>812052</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>806020</t>
+          <t>882244</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>59,17%</t>
+          <t>59,39%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>56,6%</t>
+          <t>57,09%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>61,54%</t>
+          <t>62,03%</t>
         </is>
       </c>
     </row>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>634412</t>
+          <t>689628</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>634412</t>
+          <t>689628</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>634412</t>
+          <t>689628</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1212,17 +1212,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>675370</t>
+          <t>732722</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>675370</t>
+          <t>732722</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>675370</t>
+          <t>732722</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1309782</t>
+          <t>1422350</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1309782</t>
+          <t>1422350</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1309782</t>
+          <t>1422350</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>80187</t>
+          <t>88354</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>40286</t>
+          <t>71389</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>112039</t>
+          <t>109827</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>109506</t>
+          <t>124260</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>94201</t>
+          <t>107966</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>125257</t>
+          <t>142179</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>189693</t>
+          <t>212614</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>125571</t>
+          <t>186803</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>222678</t>
+          <t>240030</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
+          <t>10,03%</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
           <t>8,82%</t>
         </is>
       </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>5,84%</t>
-        </is>
-      </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>11,33%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>65884</t>
+          <t>74576</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>33484</t>
+          <t>58041</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>94022</t>
+          <t>96868</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>102049</t>
+          <t>112667</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>87305</t>
+          <t>96317</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>119896</t>
+          <t>130281</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>167933</t>
+          <t>187243</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>108920</t>
+          <t>162990</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>199331</t>
+          <t>215874</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>10,19%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>136656</t>
+          <t>157707</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>64213</t>
+          <t>134615</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>180023</t>
+          <t>184565</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>221180</t>
+          <t>244017</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>200699</t>
+          <t>223567</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>241819</t>
+          <t>267481</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>23,09%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>20,88%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>25,24%</t>
+          <t>24,98%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>357836</t>
+          <t>401724</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>243282</t>
+          <t>371695</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>418363</t>
+          <t>437980</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>18,96%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>20,67%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>909168</t>
+          <t>727292</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>822346</t>
+          <t>692547</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1063336</t>
+          <t>758202</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>76,28%</t>
+          <t>69,4%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>68,99%</t>
+          <t>66,09%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>89,21%</t>
+          <t>72,35%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>525371</t>
+          <t>589894</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>500155</t>
+          <t>559957</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>552665</t>
+          <t>620237</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>54,83%</t>
+          <t>55,09%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>52,2%</t>
+          <t>52,29%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>57,68%</t>
+          <t>57,92%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1434540</t>
+          <t>1317186</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1328133</t>
+          <t>1271760</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1676785</t>
+          <t>1359126</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>66,72%</t>
+          <t>62,17%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>61,77%</t>
+          <t>60,02%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>77,99%</t>
+          <t>64,15%</t>
         </is>
       </c>
     </row>
@@ -1746,17 +1746,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1191895</t>
+          <t>1047929</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1191895</t>
+          <t>1047929</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1191895</t>
+          <t>1047929</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>958106</t>
+          <t>1070838</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>958106</t>
+          <t>1070838</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>958106</t>
+          <t>1070838</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>2150002</t>
+          <t>2118767</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2150002</t>
+          <t>2118767</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2150002</t>
+          <t>2118767</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>46705</t>
+          <t>50331</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>34352</t>
+          <t>36956</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>63992</t>
+          <t>67386</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>57188</t>
+          <t>65337</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>26627</t>
+          <t>52689</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>78358</t>
+          <t>80503</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>103893</t>
+          <t>115668</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>70723</t>
+          <t>96121</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>131204</t>
+          <t>138794</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>8,59%</t>
         </is>
       </c>
     </row>
@@ -1976,32 +1976,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>40810</t>
+          <t>45955</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>29572</t>
+          <t>34529</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>53836</t>
+          <t>61164</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2011,32 +2011,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>74966</t>
+          <t>87162</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>35847</t>
+          <t>73342</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>103034</t>
+          <t>105751</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>115777</t>
+          <t>133117</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>74464</t>
+          <t>116564</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>140993</t>
+          <t>158032</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>9,78%</t>
         </is>
       </c>
     </row>
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>134031</t>
+          <t>147141</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>111986</t>
+          <t>125883</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>162107</t>
+          <t>176160</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>21,94%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>119266</t>
+          <t>139939</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>59967</t>
+          <t>122913</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>161489</t>
+          <t>159741</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>17,23%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>253297</t>
+          <t>287080</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>162135</t>
+          <t>256552</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>302804</t>
+          <t>319891</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>17,77%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>19,8%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>483133</t>
+          <t>559646</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>455108</t>
+          <t>531631</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>509951</t>
+          <t>586198</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>68,56%</t>
+          <t>69,69%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>64,58%</t>
+          <t>66,2%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>72,37%</t>
+          <t>72,99%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>681946</t>
+          <t>519821</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>599720</t>
+          <t>493124</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>807164</t>
+          <t>542878</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>73,06%</t>
+          <t>64,0%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>64,25%</t>
+          <t>60,71%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>86,48%</t>
+          <t>66,84%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1165079</t>
+          <t>1079467</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1083070</t>
+          <t>1038267</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1328078</t>
+          <t>1117436</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>71,13%</t>
+          <t>66,83%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>66,12%</t>
+          <t>64,28%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>81,08%</t>
+          <t>69,18%</t>
         </is>
       </c>
     </row>
@@ -2315,17 +2315,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2350,17 +2350,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2432,32 +2432,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>91649</t>
+          <t>101591</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>73196</t>
+          <t>83730</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>111181</t>
+          <t>122350</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2467,32 +2467,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>118907</t>
+          <t>134438</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>95298</t>
+          <t>116851</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>142906</t>
+          <t>152034</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>210556</t>
+          <t>236028</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>182034</t>
+          <t>210340</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>239036</t>
+          <t>260726</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>12,37%</t>
         </is>
       </c>
     </row>
@@ -2545,32 +2545,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>82074</t>
+          <t>83170</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>66522</t>
+          <t>66660</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>101777</t>
+          <t>101279</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2580,32 +2580,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>120284</t>
+          <t>130919</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>97456</t>
+          <t>113323</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>140694</t>
+          <t>149230</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>202357</t>
+          <t>214088</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>176318</t>
+          <t>189197</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>231188</t>
+          <t>239238</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,35%</t>
         </is>
       </c>
     </row>
@@ -2658,32 +2658,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>144088</t>
+          <t>153217</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>126450</t>
+          <t>131451</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>169399</t>
+          <t>177065</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>17,88%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2693,32 +2693,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>186556</t>
+          <t>203836</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>149881</t>
+          <t>183855</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>209767</t>
+          <t>228245</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>20,41%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2728,32 +2728,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>330645</t>
+          <t>357053</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>293251</t>
+          <t>326580</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>365496</t>
+          <t>390670</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,93%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>18,53%</t>
         </is>
       </c>
     </row>
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>609019</t>
+          <t>652085</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>576538</t>
+          <t>621478</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>637736</t>
+          <t>679320</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>65,71%</t>
+          <t>65,86%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>62,21%</t>
+          <t>62,77%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>68,81%</t>
+          <t>68,61%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>666847</t>
+          <t>649127</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>625063</t>
+          <t>618960</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>750717</t>
+          <t>675627</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>61,03%</t>
+          <t>58,04%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>57,21%</t>
+          <t>55,35%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>68,71%</t>
+          <t>60,41%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1275866</t>
+          <t>1301211</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1225655</t>
+          <t>1259181</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1362434</t>
+          <t>1339148</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>63,18%</t>
+          <t>61,72%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>60,69%</t>
+          <t>59,72%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>67,47%</t>
+          <t>63,52%</t>
         </is>
       </c>
     </row>
@@ -2884,17 +2884,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,17 +2919,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>1092593</t>
+          <t>1118319</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1092593</t>
+          <t>1118319</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1092593</t>
+          <t>1118319</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>2019424</t>
+          <t>2108381</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2019424</t>
+          <t>2108381</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2019424</t>
+          <t>2108381</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3001,32 +3001,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>265973</t>
+          <t>292352</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>202431</t>
+          <t>260031</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>305232</t>
+          <t>327369</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3036,32 +3036,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>354214</t>
+          <t>400453</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>289864</t>
+          <t>369211</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>393274</t>
+          <t>430684</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3071,32 +3071,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>620187</t>
+          <t>692806</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>534790</t>
+          <t>652314</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>679143</t>
+          <t>741865</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>10,21%</t>
         </is>
       </c>
     </row>
@@ -3114,32 +3114,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>234357</t>
+          <t>253081</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>187849</t>
+          <t>222458</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>271955</t>
+          <t>286683</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3149,32 +3149,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>380283</t>
+          <t>421648</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>316061</t>
+          <t>392528</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>421723</t>
+          <t>460424</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3184,32 +3184,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>614640</t>
+          <t>674729</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>534577</t>
+          <t>629565</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>674359</t>
+          <t>723269</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,96%</t>
         </is>
       </c>
     </row>
@@ -3227,32 +3227,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>533412</t>
+          <t>586479</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>416339</t>
+          <t>537915</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>596112</t>
+          <t>632500</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3262,32 +3262,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>698561</t>
+          <t>768165</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>569538</t>
+          <t>726975</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>763516</t>
+          <t>809251</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>21,67%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3297,32 +3297,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1231973</t>
+          <t>1354644</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1066915</t>
+          <t>1295799</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1322797</t>
+          <t>1420784</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>18,65%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>19,56%</t>
         </is>
       </c>
     </row>
@@ -3340,32 +3340,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>2424076</t>
+          <t>2398780</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2323094</t>
+          <t>2334855</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2679751</t>
+          <t>2457467</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>70,1%</t>
+          <t>67,94%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>67,18%</t>
+          <t>66,13%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>77,5%</t>
+          <t>69,6%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3375,32 +3375,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>2226377</t>
+          <t>2143871</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>2108351</t>
+          <t>2087037</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>2476478</t>
+          <t>2194718</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>60,84%</t>
+          <t>57,41%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>57,61%</t>
+          <t>55,89%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>67,67%</t>
+          <t>58,77%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3410,32 +3410,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>4650453</t>
+          <t>4542651</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>4490366</t>
+          <t>4457001</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>4975461</t>
+          <t>4618111</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>65,34%</t>
+          <t>62,53%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>63,09%</t>
+          <t>61,35%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>69,91%</t>
+          <t>63,57%</t>
         </is>
       </c>
     </row>
@@ -3453,17 +3453,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>3457818</t>
+          <t>3530692</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>3457818</t>
+          <t>3530692</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>3457818</t>
+          <t>3530692</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>3659435</t>
+          <t>3734137</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>3659435</t>
+          <t>3734137</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3659435</t>
+          <t>3734137</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>7117253</t>
+          <t>7264830</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>7117253</t>
+          <t>7264830</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>7117253</t>
+          <t>7264830</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
